--- a/evaluation_forms/021_virtual_care_workflow_assessment_evaluation_form--evaluation_forms.xlsx
+++ b/evaluation_forms/021_virtual_care_workflow_assessment_evaluation_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Patient Satisfaction Hospital</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Staff Safety Concerns</t>
+          <t>Staff Safety Concerns Improvement</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>staff_safety_concerns_improvement</t>
+          <t>staff_safety_concerns_improvement_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Staff Safety Concerns Improvement</t>
+          <t>Staff Safety Concerns Improvement 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>service_availability_improvement</t>
+          <t>service_availability_improvement_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Service Availability Improvement</t>
+          <t>Service Availability Improvement 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>patient_satisfaction_improvement</t>
+          <t>patient_satisfaction_improvement_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Patient Satisfaction Improvement</t>
+          <t>Patient Satisfaction Improvement 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -986,7 +986,7 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="43" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1215,7 +1215,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>staff_safety_concerns_improvement_choices</t>
+          <t>staff_safety_concerns_improvement_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1232,7 +1232,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>staff_safety_concerns_improvement_choices</t>
+          <t>staff_safety_concerns_improvement_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>service_availability_improvement_choices</t>
+          <t>service_availability_improvement_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1266,7 +1266,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>service_availability_improvement_choices</t>
+          <t>service_availability_improvement_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>patient_satisfaction_improvement_choices</t>
+          <t>patient_satisfaction_improvement_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1300,7 +1300,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>patient_satisfaction_improvement_choices</t>
+          <t>patient_satisfaction_improvement_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
